--- a/cet4/result/88_音乐女神_琴键梦想的逆袭/88_音乐女神_琴键梦想的逆袭_学习版.xlsx
+++ b/cet4/result/88_音乐女神_琴键梦想的逆袭/88_音乐女神_琴键梦想的逆袭_学习版.xlsx
@@ -399,710 +399,710 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D50"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>sacred</v>
       </c>
       <c r="B2" t="str">
-        <v>sacred</v>
+        <v>/ˈseɪkrɪd/</v>
       </c>
       <c r="C2" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>神圣的</v>
       </c>
-      <c r="D2" t="str">
-        <v>sacred(神圣的)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>messenger</v>
       </c>
       <c r="B3" t="str">
-        <v>messenger</v>
+        <v>/ˈmesɪndʒər/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>传递者</v>
       </c>
-      <c r="D3" t="str">
-        <v>messenger(传递者)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>fall</v>
       </c>
       <c r="B4" t="str">
-        <v>fall</v>
+        <v>/fɔːl/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>落叶</v>
       </c>
-      <c r="D4" t="str">
-        <v>fall(落叶)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>week</v>
       </c>
       <c r="B5" t="str">
-        <v>week</v>
+        <v>/wiːk/</v>
       </c>
       <c r="C5" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>周</v>
       </c>
-      <c r="D5" t="str">
-        <v>week(周)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>examine</v>
       </c>
       <c r="B6" t="str">
-        <v>examine</v>
+        <v>/ɪɡˈzæmɪn/</v>
       </c>
       <c r="C6" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D6" t="str">
         <v>检查</v>
       </c>
-      <c r="D6" t="str">
-        <v>examine(检查)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>spider</v>
       </c>
       <c r="B7" t="str">
-        <v>spider</v>
+        <v>/ˈspaɪdər/</v>
       </c>
       <c r="C7" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>蜘蛛</v>
       </c>
-      <c r="D7" t="str">
-        <v>spider(蜘蛛)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>preposition</v>
       </c>
       <c r="B8" t="str">
-        <v>preposition</v>
+        <v>/ˌprepəˈzɪʃn/</v>
       </c>
       <c r="C8" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>介词</v>
       </c>
-      <c r="D8" t="str">
-        <v>preposition(介词)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>foremost</v>
       </c>
       <c r="B9" t="str">
-        <v>foremost</v>
+        <v>/ˈfɔːrmoʊst/</v>
       </c>
       <c r="C9" t="str">
+        <v>v./adj./adv.</v>
+      </c>
+      <c r="D9" t="str">
         <v>最重要的</v>
       </c>
-      <c r="D9" t="str">
-        <v>foremost(最重要的)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>vision</v>
       </c>
       <c r="B10" t="str">
-        <v>vision</v>
+        <v>/ˈvɪʒn/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D10" t="str">
         <v>愿景</v>
       </c>
-      <c r="D10" t="str">
-        <v>vision(愿景)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>chess</v>
       </c>
       <c r="B11" t="str">
-        <v>chess</v>
+        <v>/tʃes/</v>
       </c>
       <c r="C11" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>下国际象棋</v>
       </c>
-      <c r="D11" t="str">
-        <v>chess(下国际象棋)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>confidence</v>
       </c>
       <c r="B12" t="str">
-        <v>confidence</v>
+        <v>/ˈkɑːnfɪdəns/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D12" t="str">
         <v>信心</v>
       </c>
-      <c r="D12" t="str">
-        <v>confidence(信心)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>empty</v>
       </c>
       <c r="B13" t="str">
-        <v>empty</v>
+        <v>/ˈempti/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D13" t="str">
         <v>空</v>
       </c>
-      <c r="D13" t="str">
-        <v>empty(空)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>lip</v>
       </c>
       <c r="B14" t="str">
-        <v>lip</v>
+        <v>/lɪp/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D14" t="str">
         <v>嘴唇</v>
       </c>
-      <c r="D14" t="str">
-        <v>lip(嘴唇)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>marine</v>
       </c>
       <c r="B15" t="str">
-        <v>marine</v>
+        <v>/məˈriːn/</v>
       </c>
       <c r="C15" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D15" t="str">
         <v>海生的</v>
       </c>
-      <c r="D15" t="str">
-        <v>marine(海生的)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>nervous</v>
       </c>
       <c r="B16" t="str">
-        <v>nervous</v>
+        <v>/ˈnɜːrvəs/</v>
       </c>
       <c r="C16" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D16" t="str">
         <v>紧张</v>
       </c>
-      <c r="D16" t="str">
-        <v>nervous(紧张)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>reverse</v>
       </c>
       <c r="B17" t="str">
-        <v>reverse</v>
+        <v>/rɪˈvɜːrs/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D17" t="str">
         <v>颠倒</v>
       </c>
-      <c r="D17" t="str">
-        <v>reverse(颠倒)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>neighbourhood</v>
       </c>
       <c r="B18" t="str">
-        <v>neighbourhood</v>
+        <v>/ˈneɪbərhʊd/</v>
       </c>
       <c r="C18" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>附近</v>
       </c>
-      <c r="D18" t="str">
-        <v>neighbourhood(附近)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>suit</v>
       </c>
       <c r="B19" t="str">
-        <v>suit</v>
+        <v>/suːt/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D19" t="str">
         <v>套装</v>
       </c>
-      <c r="D19" t="str">
-        <v>suit(套装)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>good</v>
       </c>
       <c r="B20" t="str">
-        <v>good</v>
+        <v>/ɡʊd/</v>
       </c>
       <c r="C20" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D20" t="str">
         <v>好</v>
       </c>
-      <c r="D20" t="str">
-        <v>good(好)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>plan</v>
       </c>
       <c r="B21" t="str">
-        <v>plan</v>
+        <v>/plæn/</v>
       </c>
       <c r="C21" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D21" t="str">
         <v>计划</v>
       </c>
-      <c r="D21" t="str">
-        <v>plan(计划)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>strawberry</v>
       </c>
       <c r="B22" t="str">
-        <v>strawberry</v>
+        <v>/ˈstrɔːberi/</v>
       </c>
       <c r="C22" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>草莓</v>
       </c>
-      <c r="D22" t="str">
-        <v>strawberry(草莓)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>strongly</v>
       </c>
       <c r="B23" t="str">
-        <v>strongly</v>
+        <v>/ˈstrɔːŋli/</v>
       </c>
       <c r="C23" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D23" t="str">
         <v>坚定地</v>
       </c>
-      <c r="D23" t="str">
-        <v>strongly(坚定地)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>net</v>
       </c>
       <c r="B24" t="str">
-        <v>net</v>
+        <v>/net/</v>
       </c>
       <c r="C24" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D24" t="str">
         <v>网</v>
       </c>
-      <c r="D24" t="str">
-        <v>net(网)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>sixth</v>
       </c>
       <c r="B25" t="str">
-        <v>sixth</v>
+        <v>/sɪksθ/</v>
       </c>
       <c r="C25" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D25" t="str">
         <v>第六</v>
       </c>
-      <c r="D25" t="str">
-        <v>sixth(第六)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>travel</v>
       </c>
       <c r="B26" t="str">
-        <v>travel</v>
+        <v>/ˈtrævl/</v>
       </c>
       <c r="C26" t="str">
+        <v>n./vi./v.</v>
+      </c>
+      <c r="D26" t="str">
         <v>旅行</v>
       </c>
-      <c r="D26" t="str">
-        <v>travel(旅行)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>stroke</v>
       </c>
       <c r="B27" t="str">
-        <v>stroke</v>
+        <v>/stroʊk/</v>
       </c>
       <c r="C27" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D27" t="str">
         <v>笔画</v>
       </c>
-      <c r="D27" t="str">
-        <v>stroke(笔画)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>any</v>
       </c>
       <c r="B28" t="str">
-        <v>any</v>
+        <v>/ˈeni/</v>
       </c>
       <c r="C28" t="str">
+        <v>n./adj./pron.</v>
+      </c>
+      <c r="D28" t="str">
         <v>任何</v>
       </c>
-      <c r="D28" t="str">
-        <v>any(任何)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>challenge</v>
       </c>
       <c r="B29" t="str">
-        <v>challenge</v>
+        <v>/ˈtʃælɪndʒ/</v>
       </c>
       <c r="C29" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D29" t="str">
         <v>挑战</v>
       </c>
-      <c r="D29" t="str">
-        <v>challenge(挑战)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>forehead</v>
       </c>
       <c r="B30" t="str">
-        <v>forehead</v>
+        <v>/ˈfɔːrhed,ˈfɔːrəd/</v>
       </c>
       <c r="C30" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>额头</v>
       </c>
-      <c r="D30" t="str">
-        <v>forehead(额头)📢</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>coffee</v>
       </c>
       <c r="B31" t="str">
-        <v>coffee</v>
+        <v>/ˈkɔːfi/</v>
       </c>
       <c r="C31" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>咖啡</v>
       </c>
-      <c r="D31" t="str">
-        <v>coffee(咖啡)📢</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>late</v>
       </c>
       <c r="B32" t="str">
-        <v>late</v>
+        <v>/leɪt/</v>
       </c>
       <c r="C32" t="str">
+        <v>v./adj./adv.</v>
+      </c>
+      <c r="D32" t="str">
         <v>很晚</v>
       </c>
-      <c r="D32" t="str">
-        <v>late(很晚)📢</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>precious</v>
       </c>
       <c r="B33" t="str">
-        <v>precious</v>
+        <v>/ˈpreʃəs/</v>
       </c>
       <c r="C33" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D33" t="str">
         <v>珍贵的</v>
       </c>
-      <c r="D33" t="str">
-        <v>precious(珍贵的)📢</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>saving</v>
       </c>
       <c r="B34" t="str">
-        <v>saving</v>
+        <v>/ˈseɪvɪŋ/</v>
       </c>
       <c r="C34" t="str">
+        <v>n./adj./prep.</v>
+      </c>
+      <c r="D34" t="str">
         <v>节省</v>
       </c>
-      <c r="D34" t="str">
-        <v>saving(节省)📢</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>most</v>
       </c>
       <c r="B35" t="str">
-        <v>most</v>
+        <v>/moʊst/</v>
       </c>
       <c r="C35" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D35" t="str">
         <v>最</v>
       </c>
-      <c r="D35" t="str">
-        <v>most(最)📢</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>drought</v>
       </c>
       <c r="B36" t="str">
-        <v>drought</v>
+        <v>/draʊt/</v>
       </c>
       <c r="C36" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D36" t="str">
         <v>干旱</v>
       </c>
-      <c r="D36" t="str">
-        <v>drought(干旱)📢</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>repeatedly</v>
       </c>
       <c r="B37" t="str">
-        <v>repeatedly</v>
+        <v>/rɪˈpiːtɪdli/</v>
       </c>
       <c r="C37" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D37" t="str">
         <v>反复</v>
       </c>
-      <c r="D37" t="str">
-        <v>repeatedly(反复)📢</v>
-      </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>habitual</v>
       </c>
       <c r="B38" t="str">
-        <v>habitual</v>
+        <v>/həˈbɪtʃuəl/</v>
       </c>
       <c r="C38" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D38" t="str">
         <v>习惯</v>
       </c>
-      <c r="D38" t="str">
-        <v>habitual(习惯)📢</v>
-      </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>isolate</v>
       </c>
       <c r="B39" t="str">
-        <v>isolate</v>
+        <v>/ˈaɪsəleɪt/</v>
       </c>
       <c r="C39" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D39" t="str">
         <v>隔离</v>
       </c>
-      <c r="D39" t="str">
-        <v>isolate(隔离)📢</v>
-      </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>born</v>
       </c>
       <c r="B40" t="str">
-        <v>born</v>
+        <v>/bɔːrn/</v>
       </c>
       <c r="C40" t="str">
+        <v>n./v./adj.</v>
+      </c>
+      <c r="D40" t="str">
         <v>生来</v>
       </c>
-      <c r="D40" t="str">
-        <v>born(生来)📢</v>
-      </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>emphasize</v>
       </c>
       <c r="B41" t="str">
-        <v>emphasize</v>
+        <v>/ˈemfəsaɪz/</v>
       </c>
       <c r="C41" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D41" t="str">
         <v>强调</v>
       </c>
-      <c r="D41" t="str">
-        <v>emphasize(强调)📢</v>
-      </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>bunch</v>
       </c>
       <c r="B42" t="str">
-        <v>bunch</v>
+        <v>/bʌntʃ/</v>
       </c>
       <c r="C42" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D42" t="str">
         <v>束</v>
       </c>
-      <c r="D42" t="str">
-        <v>bunch(束)📢</v>
-      </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>obviously</v>
       </c>
       <c r="B43" t="str">
-        <v>obviously</v>
+        <v>/ˈɑːbviəsli/</v>
       </c>
       <c r="C43" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D43" t="str">
         <v>明显</v>
       </c>
-      <c r="D43" t="str">
-        <v>obviously(明显)📢</v>
-      </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>watch</v>
       </c>
       <c r="B44" t="str">
-        <v>watch</v>
+        <v>/wɑːtʃ/</v>
       </c>
       <c r="C44" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D44" t="str">
         <v>手表</v>
       </c>
-      <c r="D44" t="str">
-        <v>watch(手表)📢</v>
-      </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>burst</v>
       </c>
       <c r="B45" t="str">
-        <v>burst</v>
+        <v>/bɜːrst/</v>
       </c>
       <c r="C45" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D45" t="str">
         <v>迸发</v>
       </c>
-      <c r="D45" t="str">
-        <v>burst(迸发)📢</v>
-      </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>inn</v>
       </c>
       <c r="B46" t="str">
-        <v>inn</v>
+        <v>/ɪn/</v>
       </c>
       <c r="C46" t="str">
+        <v>n./vi.</v>
+      </c>
+      <c r="D46" t="str">
         <v>旅馆</v>
       </c>
-      <c r="D46" t="str">
-        <v>inn(旅馆)📢</v>
-      </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>corridor</v>
       </c>
       <c r="B47" t="str">
-        <v>corridor</v>
+        <v>/ˈkɔːrɪdɔːr/</v>
       </c>
       <c r="C47" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D47" t="str">
         <v>走廊</v>
       </c>
-      <c r="D47" t="str">
-        <v>corridor(走廊)📢</v>
-      </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>relation</v>
       </c>
       <c r="B48" t="str">
-        <v>relation</v>
+        <v>/rɪˈleɪʃn/</v>
       </c>
       <c r="C48" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D48" t="str">
         <v>关系</v>
       </c>
-      <c r="D48" t="str">
-        <v>relation(关系)📢</v>
-      </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>plastic</v>
       </c>
       <c r="B49" t="str">
-        <v>plastic</v>
+        <v>/ˈplæstɪk/</v>
       </c>
       <c r="C49" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D49" t="str">
         <v>塑料</v>
       </c>
-      <c r="D49" t="str">
-        <v>plastic(塑料)📢</v>
-      </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>sugar</v>
       </c>
       <c r="B50" t="str">
-        <v>sugar</v>
+        <v>/ˈʃʊɡər/</v>
       </c>
       <c r="C50" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D50" t="str">
         <v>糖</v>
-      </c>
-      <c r="D50" t="str">
-        <v>sugar(糖)📢</v>
       </c>
     </row>
   </sheetData>
